--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.65299</v>
+        <v>16.61148</v>
       </c>
       <c r="D2" t="n">
-        <v>16.45482</v>
+        <v>16.2913</v>
       </c>
       <c r="E2" t="n">
-        <v>16.47888</v>
+        <v>16.33331</v>
       </c>
       <c r="F2" t="n">
-        <v>42.34017</v>
+        <v>42.33893</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05026</v>
+        <v>0.0499</v>
       </c>
       <c r="H2" t="n">
-        <v>1.76372</v>
+        <v>1.78168</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.41835</v>
+        <v>16.81724</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47324</v>
+        <v>16.42227</v>
       </c>
       <c r="E3" t="n">
-        <v>16.53474</v>
+        <v>16.71389</v>
       </c>
       <c r="F3" t="n">
-        <v>42.32418</v>
+        <v>42.12951</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04981</v>
+        <v>0.04954</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80215</v>
+        <v>1.79414</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.7436</v>
+        <v>16.87339</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6621</v>
+        <v>16.28518</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72785</v>
+        <v>16.61568</v>
       </c>
       <c r="F4" t="n">
-        <v>41.76461</v>
+        <v>42.09407</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04914</v>
+        <v>0.05073</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81674</v>
+        <v>1.8383</v>
       </c>
     </row>
   </sheetData>
